--- a/Lab/Nested-if_&_count-sum_variants - Format.xlsx
+++ b/Lab/Nested-if_&_count-sum_variants - Format.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6800" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sales_Data" sheetId="1" r:id="rId1"/>
@@ -2885,7 +2885,9 @@
     <col min="19" max="19" width="18" style="1" customWidth="1"/>
     <col min="20" max="20" width="55" style="1" customWidth="1"/>
     <col min="21" max="21" width="28" style="1" customWidth="1"/>
-    <col min="22" max="22" width="20" style="1" customWidth="1"/>
+    <col min="22" max="22" width="18.8" style="1" customWidth="1"/>
+    <col min="23" max="23" width="12.6272727272727" customWidth="1"/>
+    <col min="24" max="24" width="12.8181818181818"/>
     <col min="25" max="25" width="71.2727272727273" customWidth="1"/>
     <col min="26" max="26" width="8.09090909090909" customWidth="1"/>
     <col min="27" max="27" width="10.3636363636364" customWidth="1"/>
@@ -3678,7 +3680,10 @@
       <c r="U11" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="V11" s="43"/>
+      <c r="V11" s="43">
+        <f>COUNTBLANK(E2:E31)</f>
+        <v>3</v>
+      </c>
       <c r="Y11" s="52" t="s">
         <v>92</v>
       </c>
@@ -3753,8 +3758,8 @@
         <v>95</v>
       </c>
       <c r="V12" s="43">
-        <f>COUNTIF(Sales_Data!D3:D32,"=Sales_Data!E3:E32")</f>
-        <v>0</v>
+        <f>COUNTIF(F2:F31,"Completed")</f>
+        <v>17</v>
       </c>
       <c r="Y12" s="52"/>
       <c r="AF12" s="51"/>
@@ -3827,7 +3832,10 @@
       <c r="U13" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="V13" s="43"/>
+      <c r="V13" s="43">
+        <f>COUNTIF(A2:B31,"West")</f>
+        <v>6</v>
+      </c>
       <c r="Y13" s="50" t="s">
         <v>98</v>
       </c>
@@ -3976,7 +3984,10 @@
       <c r="U15" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="V15" s="43"/>
+      <c r="V15" s="43">
+        <f>COUNTIF(D2:D31,"Furniture")</f>
+        <v>6</v>
+      </c>
       <c r="Y15" s="50" t="s">
         <v>102</v>
       </c>
@@ -4050,7 +4061,10 @@
       <c r="U16" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="V16" s="43"/>
+      <c r="V16" s="43">
+        <f>COUNTIFS(F2:F31,"completed",D2:D31,"Clothing")</f>
+        <v>1</v>
+      </c>
       <c r="Y16" s="66"/>
       <c r="Z16" s="67"/>
       <c r="AA16" s="67"/>
@@ -4060,7 +4074,7 @@
       <c r="AE16" s="67"/>
       <c r="AF16" s="68"/>
     </row>
-    <row r="17" ht="37.5" customHeight="1" spans="1:22">
+    <row r="17" ht="37.5" customHeight="1" spans="1:23">
       <c r="A17" s="33" t="s">
         <v>34</v>
       </c>
@@ -4126,9 +4140,12 @@
       <c r="U17" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="V17" s="43"/>
-    </row>
-    <row r="18" ht="33" customHeight="1" spans="1:22">
+      <c r="V17" s="43">
+        <f>COUNTIFS(B2:B31,"South",E2:E31,"&gt;40000")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="33" customHeight="1" spans="1:23">
       <c r="A18" s="22" t="s">
         <v>35</v>
       </c>
@@ -4196,9 +4213,12 @@
       <c r="U18" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="V18" s="43"/>
-    </row>
-    <row r="19" ht="59" customHeight="1" spans="1:22">
+      <c r="V18" s="43">
+        <f>COUNTIFS(D2:D31,"Electronics",F2:F31,"Cancelled")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="59" customHeight="1" spans="1:23">
       <c r="A19" s="33" t="s">
         <v>36</v>
       </c>
@@ -4266,9 +4286,12 @@
       <c r="U19" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="V19" s="43"/>
-    </row>
-    <row r="20" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V19" s="43">
+        <f>SUMIF(F2:F31,"Completed",E2:E31)</f>
+        <v>840139</v>
+      </c>
+    </row>
+    <row r="20" ht="37.5" customHeight="1" spans="1:23">
       <c r="A20" s="22" t="s">
         <v>37</v>
       </c>
@@ -4336,9 +4359,12 @@
       <c r="U20" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="V20" s="43"/>
-    </row>
-    <row r="21" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V20" s="43">
+        <f>SUMIF(B2:B31,"Central",E2:E31)</f>
+        <v>324281</v>
+      </c>
+    </row>
+    <row r="21" ht="37.5" customHeight="1" spans="1:23">
       <c r="A21" s="33" t="s">
         <v>38</v>
       </c>
@@ -4406,9 +4432,12 @@
       <c r="U21" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="V21" s="43"/>
-    </row>
-    <row r="22" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V21" s="43">
+        <f>SUMIF(D2:D31,"Groceries",E2:E31)</f>
+        <v>387563</v>
+      </c>
+    </row>
+    <row r="22" ht="37.5" customHeight="1" spans="1:23">
       <c r="A22" s="22" t="s">
         <v>39</v>
       </c>
@@ -4476,9 +4505,12 @@
       <c r="U22" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="V22" s="43"/>
-    </row>
-    <row r="23" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V22" s="43">
+        <f>SUMIFS(E2:E31,B2:B31,"North",F2:F31,"Completed")</f>
+        <v>207926</v>
+      </c>
+    </row>
+    <row r="23" ht="37.5" customHeight="1" spans="1:23">
       <c r="A23" s="33" t="s">
         <v>40</v>
       </c>
@@ -4546,9 +4578,12 @@
       <c r="U23" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="V23" s="43"/>
-    </row>
-    <row r="24" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V23" s="43">
+        <f>SUMIFS(E2:E31,D2:D31,"Electronics",F2:F31,"completed")</f>
+        <v>207926</v>
+      </c>
+    </row>
+    <row r="24" ht="37.5" customHeight="1" spans="1:23">
       <c r="A24" s="22" t="s">
         <v>41</v>
       </c>
@@ -4618,8 +4653,12 @@
         <f>SUMIFS(E2:E31,B2:B31,"west",E2:E31,"&gt;30000",E2:E31,"&lt;80000")</f>
         <v>112285</v>
       </c>
-    </row>
-    <row r="25" ht="37.5" customHeight="1" spans="1:22">
+      <c r="W24">
+        <f>SUMIFS(E2:E31,B2:B31,"West",E2:E31,"&gt;30000",E2:E31,"&lt;80000")</f>
+        <v>112285</v>
+      </c>
+    </row>
+    <row r="25" ht="37.5" customHeight="1" spans="1:23">
       <c r="A25" s="33" t="s">
         <v>42</v>
       </c>
@@ -4688,11 +4727,11 @@
         <v>116</v>
       </c>
       <c r="V25" s="43">
-        <f>SUMIFS(E2:E31,D2:D31,"Furniture",B2:B31,"east",F2:F31,"completed")</f>
+        <f>SUMIFS(E2:E31,D2:D31,"Furniture",B2:B31,"East",F2:F31,"completed")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="37.5" customHeight="1" spans="1:22">
+    <row r="26" ht="37.5" customHeight="1" spans="1:23">
       <c r="A26" s="22" t="s">
         <v>43</v>
       </c>
@@ -4760,9 +4799,12 @@
       <c r="U26" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="V26" s="43"/>
-    </row>
-    <row r="27" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V26" s="43">
+        <f>SUMIF(F2:F31,"Completed",E2:E31)/COUNTIF(F2:F31,"Completed")</f>
+        <v>49419.9411764706</v>
+      </c>
+    </row>
+    <row r="27" ht="37.5" customHeight="1" spans="1:23">
       <c r="A27" s="33" t="s">
         <v>44</v>
       </c>
@@ -4830,9 +4872,12 @@
       <c r="U27" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="V27" s="43"/>
-    </row>
-    <row r="28" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V27" s="43">
+        <f>COUNTIFS(E2:E31,"&gt;60000",F2:F31,"Completed")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="37.5" customHeight="1" spans="1:23">
       <c r="A28" s="22" t="s">
         <v>45</v>
       </c>
@@ -4900,9 +4945,12 @@
       <c r="U28" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="V28" s="43"/>
-    </row>
-    <row r="29" ht="37.5" customHeight="1" spans="1:22">
+      <c r="V28" s="43">
+        <f>SUMIF(F2:F31,"completed",E2:E31)</f>
+        <v>840139</v>
+      </c>
+    </row>
+    <row r="29" ht="37.5" customHeight="1" spans="1:23">
       <c r="A29" s="33" t="s">
         <v>46</v>
       </c>
@@ -4964,7 +5012,7 @@
       <c r="U29"/>
       <c r="V29"/>
     </row>
-    <row r="30" ht="37.5" customHeight="1" spans="1:22">
+    <row r="30" ht="37.5" customHeight="1" spans="1:23">
       <c r="A30" s="22" t="s">
         <v>47</v>
       </c>
@@ -5026,7 +5074,7 @@
       <c r="U30"/>
       <c r="V30"/>
     </row>
-    <row r="31" ht="37.5" customHeight="1" spans="1:22">
+    <row r="31" ht="37.5" customHeight="1" spans="1:23">
       <c r="A31" s="33" t="s">
         <v>48</v>
       </c>
@@ -5088,7 +5136,7 @@
       <c r="U31"/>
       <c r="V31"/>
     </row>
-    <row r="32" ht="37.5" customHeight="1" spans="1:22">
+    <row r="32" ht="37.5" customHeight="1" spans="1:23">
       <c r="P32"/>
       <c r="Q32"/>
       <c r="R32"/>
@@ -5110,7 +5158,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{afaac6ee-9b50-4b1a-82f0-e7eaa4781e68}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{e579848b-3db1-49ad-87e5-d8f89d9e25e0}">
             <xm:f>NOT(ISERROR(SEARCH($D$19,D1)))</xm:f>
             <xm:f>$D$19</xm:f>
             <x14:dxf>
@@ -5124,7 +5172,7 @@
           <xm:sqref>D1</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{d5a551db-7204-40eb-9d1a-78c75531302d}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{e7d37099-9f76-49d0-b70a-094a7bc70a8b}">
             <xm:f>NOT(ISERROR(SEARCH($B$21,B2)))</xm:f>
             <xm:f>$B$21</xm:f>
             <x14:dxf>
